--- a/Data/EC/NIT-9010286364.xlsx
+++ b/Data/EC/NIT-9010286364.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8321BA16-FCC9-4274-8203-8B5C272956D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9771E5E9-E197-481D-85D8-4438920EE662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{065E1E77-E653-4DF6-A858-EB568712415B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8FF28A49-156F-48F3-AE1F-982CD98475C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -662,22 +662,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F1D552-541F-7E73-B259-53CE9B09968E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4FB6620-25D1-F5AC-CD09-FE62E7F6ABFA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -686,7 +686,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -699,7 +699,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1028,23 +1028,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553AD061-D73C-435E-AC51-BC6E7F56B045}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC58B38-8725-421C-904F-E9D7D7CC9118}">
   <dimension ref="B2:J466"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1057,7 +1057,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1068,7 +1068,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1079,7 +1079,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1090,8 +1090,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>76</v>
       </c>
@@ -1106,8 +1106,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1122,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>77</v>
       </c>
@@ -1138,8 +1138,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>78</v>
       </c>
@@ -1158,7 +1158,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1210,7 +1210,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1256,7 +1256,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1279,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1325,7 +1325,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1348,7 +1348,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1371,7 +1371,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1394,7 +1394,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1417,7 +1417,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1440,7 +1440,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1463,7 +1463,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1486,7 +1486,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1578,7 +1578,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1647,7 +1647,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1670,7 +1670,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1693,7 +1693,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1716,7 +1716,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1739,7 +1739,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1762,7 +1762,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1785,7 +1785,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1808,7 +1808,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1831,7 +1831,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1854,7 +1854,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1877,7 +1877,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1923,7 +1923,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1946,7 +1946,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1969,7 +1969,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +1992,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2015,7 +2015,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2038,7 +2038,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2061,7 +2061,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2084,7 +2084,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2130,7 +2130,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2176,7 +2176,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2199,7 +2199,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2245,7 +2245,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2268,7 +2268,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2291,7 +2291,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2314,7 +2314,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2337,7 +2337,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2360,7 +2360,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2383,7 +2383,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2406,7 +2406,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2429,7 +2429,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2475,7 +2475,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2521,7 +2521,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2544,7 +2544,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2567,7 +2567,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2613,7 +2613,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2636,7 +2636,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2659,7 +2659,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2682,7 +2682,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2705,7 +2705,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2728,7 +2728,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2797,7 +2797,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2843,7 +2843,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2866,7 +2866,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2889,7 +2889,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2912,7 +2912,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2935,7 +2935,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2958,7 +2958,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2981,7 +2981,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3004,7 +3004,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3027,7 +3027,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3050,7 +3050,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3096,7 +3096,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3119,7 +3119,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3142,7 +3142,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3165,7 +3165,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3188,7 +3188,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3211,7 +3211,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3234,7 +3234,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3257,7 +3257,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3280,7 +3280,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3326,7 +3326,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3349,7 +3349,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3372,7 +3372,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3395,7 +3395,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3418,7 +3418,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3441,7 +3441,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3464,7 +3464,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3487,7 +3487,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3510,7 +3510,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3533,7 +3533,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3579,7 +3579,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3602,7 +3602,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3625,7 +3625,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3648,7 +3648,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3671,7 +3671,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3694,7 +3694,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3717,7 +3717,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3740,7 +3740,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3786,7 +3786,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3809,7 +3809,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3832,7 +3832,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3855,7 +3855,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3924,7 +3924,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3970,7 +3970,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -3993,7 +3993,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4016,7 +4016,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4039,7 +4039,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4062,7 +4062,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4085,7 +4085,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4108,7 +4108,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4131,7 +4131,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4154,7 +4154,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4177,7 +4177,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4200,7 +4200,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4223,7 +4223,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4246,7 +4246,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4269,7 +4269,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4292,7 +4292,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4315,7 +4315,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4361,7 +4361,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4384,7 +4384,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4407,7 +4407,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4453,7 +4453,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4476,7 +4476,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4522,7 +4522,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4545,7 +4545,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4568,7 +4568,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4591,7 +4591,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4614,7 +4614,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4660,7 +4660,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4683,7 +4683,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4706,7 +4706,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4729,7 +4729,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4752,7 +4752,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4775,7 +4775,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4798,7 +4798,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4821,7 +4821,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4844,7 +4844,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -4867,7 +4867,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -4890,7 +4890,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -4913,7 +4913,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -4936,7 +4936,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -4959,7 +4959,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
@@ -4982,7 +4982,7 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
@@ -5005,7 +5005,7 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
@@ -5028,7 +5028,7 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
@@ -5051,7 +5051,7 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
@@ -5074,7 +5074,7 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
@@ -5097,7 +5097,7 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
@@ -5120,7 +5120,7 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
@@ -5143,7 +5143,7 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
@@ -5166,7 +5166,7 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
@@ -5189,7 +5189,7 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
@@ -5258,7 +5258,7 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
@@ -5281,7 +5281,7 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
@@ -5304,7 +5304,7 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
@@ -5327,7 +5327,7 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
@@ -5350,7 +5350,7 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
@@ -5373,7 +5373,7 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
@@ -5396,7 +5396,7 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
@@ -5419,7 +5419,7 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
@@ -5442,7 +5442,7 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
@@ -5465,7 +5465,7 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
@@ -5488,7 +5488,7 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
@@ -5511,7 +5511,7 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
@@ -5534,7 +5534,7 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
@@ -5557,7 +5557,7 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
@@ -5580,7 +5580,7 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
@@ -5603,7 +5603,7 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
@@ -5626,7 +5626,7 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
@@ -5649,7 +5649,7 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
@@ -5672,7 +5672,7 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
@@ -5695,7 +5695,7 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
@@ -5718,7 +5718,7 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
@@ -5741,7 +5741,7 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
@@ -5764,7 +5764,7 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
@@ -5787,7 +5787,7 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
@@ -5810,7 +5810,7 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
@@ -5833,7 +5833,7 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
@@ -5856,7 +5856,7 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
@@ -5879,7 +5879,7 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
@@ -5902,7 +5902,7 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
@@ -5948,7 +5948,7 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
@@ -5971,7 +5971,7 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
@@ -5994,7 +5994,7 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
@@ -6017,7 +6017,7 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
@@ -6040,7 +6040,7 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
@@ -6063,7 +6063,7 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
@@ -6086,7 +6086,7 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
@@ -6109,7 +6109,7 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
@@ -6132,7 +6132,7 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
@@ -6155,7 +6155,7 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
@@ -6178,7 +6178,7 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
@@ -6201,7 +6201,7 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
@@ -6224,7 +6224,7 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
@@ -6247,7 +6247,7 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
@@ -6270,7 +6270,7 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
@@ -6293,7 +6293,7 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
@@ -6316,7 +6316,7 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
@@ -6339,7 +6339,7 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="15" t="s">
         <v>8</v>
       </c>
@@ -6362,7 +6362,7 @@
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" s="15" t="s">
         <v>8</v>
       </c>
@@ -6385,7 +6385,7 @@
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" s="15" t="s">
         <v>8</v>
       </c>
@@ -6408,7 +6408,7 @@
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" s="15" t="s">
         <v>8</v>
       </c>
@@ -6431,7 +6431,7 @@
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" s="15" t="s">
         <v>8</v>
       </c>
@@ -6454,7 +6454,7 @@
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="15" t="s">
         <v>8</v>
       </c>
@@ -6477,7 +6477,7 @@
       <c r="I245" s="19"/>
       <c r="J245" s="20"/>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" s="15" t="s">
         <v>8</v>
       </c>
@@ -6500,7 +6500,7 @@
       <c r="I246" s="19"/>
       <c r="J246" s="20"/>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B247" s="15" t="s">
         <v>8</v>
       </c>
@@ -6523,7 +6523,7 @@
       <c r="I247" s="19"/>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B248" s="15" t="s">
         <v>8</v>
       </c>
@@ -6546,7 +6546,7 @@
       <c r="I248" s="19"/>
       <c r="J248" s="20"/>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B249" s="15" t="s">
         <v>8</v>
       </c>
@@ -6569,7 +6569,7 @@
       <c r="I249" s="19"/>
       <c r="J249" s="20"/>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" s="15" t="s">
         <v>8</v>
       </c>
@@ -6592,7 +6592,7 @@
       <c r="I250" s="19"/>
       <c r="J250" s="20"/>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" s="15" t="s">
         <v>8</v>
       </c>
@@ -6615,7 +6615,7 @@
       <c r="I251" s="19"/>
       <c r="J251" s="20"/>
     </row>
-    <row r="252" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B252" s="15" t="s">
         <v>8</v>
       </c>
@@ -6638,7 +6638,7 @@
       <c r="I252" s="19"/>
       <c r="J252" s="20"/>
     </row>
-    <row r="253" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B253" s="15" t="s">
         <v>8</v>
       </c>
@@ -6661,7 +6661,7 @@
       <c r="I253" s="19"/>
       <c r="J253" s="20"/>
     </row>
-    <row r="254" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B254" s="15" t="s">
         <v>8</v>
       </c>
@@ -6684,7 +6684,7 @@
       <c r="I254" s="19"/>
       <c r="J254" s="20"/>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B255" s="15" t="s">
         <v>8</v>
       </c>
@@ -6707,7 +6707,7 @@
       <c r="I255" s="19"/>
       <c r="J255" s="20"/>
     </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B256" s="15" t="s">
         <v>8</v>
       </c>
@@ -6730,7 +6730,7 @@
       <c r="I256" s="19"/>
       <c r="J256" s="20"/>
     </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B257" s="15" t="s">
         <v>8</v>
       </c>
@@ -6753,7 +6753,7 @@
       <c r="I257" s="19"/>
       <c r="J257" s="20"/>
     </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B258" s="15" t="s">
         <v>8</v>
       </c>
@@ -6776,7 +6776,7 @@
       <c r="I258" s="19"/>
       <c r="J258" s="20"/>
     </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B259" s="15" t="s">
         <v>8</v>
       </c>
@@ -6799,7 +6799,7 @@
       <c r="I259" s="19"/>
       <c r="J259" s="20"/>
     </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B260" s="15" t="s">
         <v>8</v>
       </c>
@@ -6822,7 +6822,7 @@
       <c r="I260" s="19"/>
       <c r="J260" s="20"/>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B261" s="15" t="s">
         <v>8</v>
       </c>
@@ -6845,7 +6845,7 @@
       <c r="I261" s="19"/>
       <c r="J261" s="20"/>
     </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B262" s="15" t="s">
         <v>8</v>
       </c>
@@ -6868,7 +6868,7 @@
       <c r="I262" s="19"/>
       <c r="J262" s="20"/>
     </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B263" s="15" t="s">
         <v>8</v>
       </c>
@@ -6891,7 +6891,7 @@
       <c r="I263" s="19"/>
       <c r="J263" s="20"/>
     </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B264" s="15" t="s">
         <v>8</v>
       </c>
@@ -6914,7 +6914,7 @@
       <c r="I264" s="19"/>
       <c r="J264" s="20"/>
     </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B265" s="15" t="s">
         <v>8</v>
       </c>
@@ -6937,7 +6937,7 @@
       <c r="I265" s="19"/>
       <c r="J265" s="20"/>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B266" s="15" t="s">
         <v>8</v>
       </c>
@@ -6960,7 +6960,7 @@
       <c r="I266" s="19"/>
       <c r="J266" s="20"/>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B267" s="15" t="s">
         <v>8</v>
       </c>
@@ -6983,7 +6983,7 @@
       <c r="I267" s="19"/>
       <c r="J267" s="20"/>
     </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B268" s="15" t="s">
         <v>8</v>
       </c>
@@ -7006,7 +7006,7 @@
       <c r="I268" s="19"/>
       <c r="J268" s="20"/>
     </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B269" s="15" t="s">
         <v>8</v>
       </c>
@@ -7029,7 +7029,7 @@
       <c r="I269" s="19"/>
       <c r="J269" s="20"/>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B270" s="15" t="s">
         <v>8</v>
       </c>
@@ -7052,7 +7052,7 @@
       <c r="I270" s="19"/>
       <c r="J270" s="20"/>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B271" s="15" t="s">
         <v>8</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="I271" s="19"/>
       <c r="J271" s="20"/>
     </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B272" s="15" t="s">
         <v>8</v>
       </c>
@@ -7098,7 +7098,7 @@
       <c r="I272" s="19"/>
       <c r="J272" s="20"/>
     </row>
-    <row r="273" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B273" s="15" t="s">
         <v>8</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="I273" s="19"/>
       <c r="J273" s="20"/>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B274" s="15" t="s">
         <v>8</v>
       </c>
@@ -7144,7 +7144,7 @@
       <c r="I274" s="19"/>
       <c r="J274" s="20"/>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B275" s="15" t="s">
         <v>8</v>
       </c>
@@ -7167,7 +7167,7 @@
       <c r="I275" s="19"/>
       <c r="J275" s="20"/>
     </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B276" s="15" t="s">
         <v>8</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="I276" s="19"/>
       <c r="J276" s="20"/>
     </row>
-    <row r="277" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B277" s="15" t="s">
         <v>8</v>
       </c>
@@ -7213,7 +7213,7 @@
       <c r="I277" s="19"/>
       <c r="J277" s="20"/>
     </row>
-    <row r="278" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B278" s="15" t="s">
         <v>8</v>
       </c>
@@ -7236,7 +7236,7 @@
       <c r="I278" s="19"/>
       <c r="J278" s="20"/>
     </row>
-    <row r="279" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B279" s="15" t="s">
         <v>8</v>
       </c>
@@ -7259,7 +7259,7 @@
       <c r="I279" s="19"/>
       <c r="J279" s="20"/>
     </row>
-    <row r="280" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B280" s="15" t="s">
         <v>8</v>
       </c>
@@ -7282,7 +7282,7 @@
       <c r="I280" s="19"/>
       <c r="J280" s="20"/>
     </row>
-    <row r="281" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B281" s="15" t="s">
         <v>8</v>
       </c>
@@ -7305,7 +7305,7 @@
       <c r="I281" s="19"/>
       <c r="J281" s="20"/>
     </row>
-    <row r="282" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B282" s="15" t="s">
         <v>8</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="I282" s="19"/>
       <c r="J282" s="20"/>
     </row>
-    <row r="283" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B283" s="15" t="s">
         <v>8</v>
       </c>
@@ -7351,7 +7351,7 @@
       <c r="I283" s="19"/>
       <c r="J283" s="20"/>
     </row>
-    <row r="284" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B284" s="15" t="s">
         <v>8</v>
       </c>
@@ -7374,7 +7374,7 @@
       <c r="I284" s="19"/>
       <c r="J284" s="20"/>
     </row>
-    <row r="285" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B285" s="15" t="s">
         <v>8</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="I285" s="19"/>
       <c r="J285" s="20"/>
     </row>
-    <row r="286" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B286" s="15" t="s">
         <v>8</v>
       </c>
@@ -7420,7 +7420,7 @@
       <c r="I286" s="19"/>
       <c r="J286" s="20"/>
     </row>
-    <row r="287" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B287" s="15" t="s">
         <v>8</v>
       </c>
@@ -7443,7 +7443,7 @@
       <c r="I287" s="19"/>
       <c r="J287" s="20"/>
     </row>
-    <row r="288" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B288" s="15" t="s">
         <v>8</v>
       </c>
@@ -7466,7 +7466,7 @@
       <c r="I288" s="19"/>
       <c r="J288" s="20"/>
     </row>
-    <row r="289" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B289" s="15" t="s">
         <v>8</v>
       </c>
@@ -7489,7 +7489,7 @@
       <c r="I289" s="19"/>
       <c r="J289" s="20"/>
     </row>
-    <row r="290" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B290" s="15" t="s">
         <v>8</v>
       </c>
@@ -7512,7 +7512,7 @@
       <c r="I290" s="19"/>
       <c r="J290" s="20"/>
     </row>
-    <row r="291" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B291" s="15" t="s">
         <v>8</v>
       </c>
@@ -7535,7 +7535,7 @@
       <c r="I291" s="19"/>
       <c r="J291" s="20"/>
     </row>
-    <row r="292" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B292" s="15" t="s">
         <v>8</v>
       </c>
@@ -7558,7 +7558,7 @@
       <c r="I292" s="19"/>
       <c r="J292" s="20"/>
     </row>
-    <row r="293" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B293" s="15" t="s">
         <v>8</v>
       </c>
@@ -7581,7 +7581,7 @@
       <c r="I293" s="19"/>
       <c r="J293" s="20"/>
     </row>
-    <row r="294" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B294" s="15" t="s">
         <v>8</v>
       </c>
@@ -7604,7 +7604,7 @@
       <c r="I294" s="19"/>
       <c r="J294" s="20"/>
     </row>
-    <row r="295" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B295" s="15" t="s">
         <v>8</v>
       </c>
@@ -7627,7 +7627,7 @@
       <c r="I295" s="19"/>
       <c r="J295" s="20"/>
     </row>
-    <row r="296" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B296" s="15" t="s">
         <v>8</v>
       </c>
@@ -7650,7 +7650,7 @@
       <c r="I296" s="19"/>
       <c r="J296" s="20"/>
     </row>
-    <row r="297" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B297" s="15" t="s">
         <v>8</v>
       </c>
@@ -7673,7 +7673,7 @@
       <c r="I297" s="19"/>
       <c r="J297" s="20"/>
     </row>
-    <row r="298" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="298" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B298" s="15" t="s">
         <v>8</v>
       </c>
@@ -7696,7 +7696,7 @@
       <c r="I298" s="19"/>
       <c r="J298" s="20"/>
     </row>
-    <row r="299" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="299" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B299" s="15" t="s">
         <v>8</v>
       </c>
@@ -7719,7 +7719,7 @@
       <c r="I299" s="19"/>
       <c r="J299" s="20"/>
     </row>
-    <row r="300" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="300" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B300" s="15" t="s">
         <v>8</v>
       </c>
@@ -7742,7 +7742,7 @@
       <c r="I300" s="19"/>
       <c r="J300" s="20"/>
     </row>
-    <row r="301" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B301" s="15" t="s">
         <v>8</v>
       </c>
@@ -7765,7 +7765,7 @@
       <c r="I301" s="19"/>
       <c r="J301" s="20"/>
     </row>
-    <row r="302" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="302" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B302" s="15" t="s">
         <v>8</v>
       </c>
@@ -7788,7 +7788,7 @@
       <c r="I302" s="19"/>
       <c r="J302" s="20"/>
     </row>
-    <row r="303" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="303" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B303" s="15" t="s">
         <v>8</v>
       </c>
@@ -7811,7 +7811,7 @@
       <c r="I303" s="19"/>
       <c r="J303" s="20"/>
     </row>
-    <row r="304" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="304" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B304" s="15" t="s">
         <v>8</v>
       </c>
@@ -7834,7 +7834,7 @@
       <c r="I304" s="19"/>
       <c r="J304" s="20"/>
     </row>
-    <row r="305" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="305" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B305" s="15" t="s">
         <v>8</v>
       </c>
@@ -7857,7 +7857,7 @@
       <c r="I305" s="19"/>
       <c r="J305" s="20"/>
     </row>
-    <row r="306" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="306" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B306" s="15" t="s">
         <v>8</v>
       </c>
@@ -7880,7 +7880,7 @@
       <c r="I306" s="19"/>
       <c r="J306" s="20"/>
     </row>
-    <row r="307" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="307" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B307" s="15" t="s">
         <v>8</v>
       </c>
@@ -7903,7 +7903,7 @@
       <c r="I307" s="19"/>
       <c r="J307" s="20"/>
     </row>
-    <row r="308" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="308" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B308" s="15" t="s">
         <v>8</v>
       </c>
@@ -7926,7 +7926,7 @@
       <c r="I308" s="19"/>
       <c r="J308" s="20"/>
     </row>
-    <row r="309" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="309" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B309" s="15" t="s">
         <v>8</v>
       </c>
@@ -7949,7 +7949,7 @@
       <c r="I309" s="19"/>
       <c r="J309" s="20"/>
     </row>
-    <row r="310" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="310" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B310" s="15" t="s">
         <v>8</v>
       </c>
@@ -7972,7 +7972,7 @@
       <c r="I310" s="19"/>
       <c r="J310" s="20"/>
     </row>
-    <row r="311" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="311" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B311" s="15" t="s">
         <v>8</v>
       </c>
@@ -7995,7 +7995,7 @@
       <c r="I311" s="19"/>
       <c r="J311" s="20"/>
     </row>
-    <row r="312" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="312" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B312" s="15" t="s">
         <v>8</v>
       </c>
@@ -8018,7 +8018,7 @@
       <c r="I312" s="19"/>
       <c r="J312" s="20"/>
     </row>
-    <row r="313" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="313" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B313" s="15" t="s">
         <v>8</v>
       </c>
@@ -8041,7 +8041,7 @@
       <c r="I313" s="19"/>
       <c r="J313" s="20"/>
     </row>
-    <row r="314" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="314" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B314" s="15" t="s">
         <v>8</v>
       </c>
@@ -8064,7 +8064,7 @@
       <c r="I314" s="19"/>
       <c r="J314" s="20"/>
     </row>
-    <row r="315" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="315" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B315" s="15" t="s">
         <v>8</v>
       </c>
@@ -8087,7 +8087,7 @@
       <c r="I315" s="19"/>
       <c r="J315" s="20"/>
     </row>
-    <row r="316" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B316" s="15" t="s">
         <v>8</v>
       </c>
@@ -8110,7 +8110,7 @@
       <c r="I316" s="19"/>
       <c r="J316" s="20"/>
     </row>
-    <row r="317" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="317" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B317" s="15" t="s">
         <v>8</v>
       </c>
@@ -8133,7 +8133,7 @@
       <c r="I317" s="19"/>
       <c r="J317" s="20"/>
     </row>
-    <row r="318" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="318" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B318" s="15" t="s">
         <v>8</v>
       </c>
@@ -8156,7 +8156,7 @@
       <c r="I318" s="19"/>
       <c r="J318" s="20"/>
     </row>
-    <row r="319" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="319" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B319" s="15" t="s">
         <v>8</v>
       </c>
@@ -8179,7 +8179,7 @@
       <c r="I319" s="19"/>
       <c r="J319" s="20"/>
     </row>
-    <row r="320" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="320" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B320" s="15" t="s">
         <v>8</v>
       </c>
@@ -8202,7 +8202,7 @@
       <c r="I320" s="19"/>
       <c r="J320" s="20"/>
     </row>
-    <row r="321" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="321" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B321" s="15" t="s">
         <v>8</v>
       </c>
@@ -8225,7 +8225,7 @@
       <c r="I321" s="19"/>
       <c r="J321" s="20"/>
     </row>
-    <row r="322" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="322" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B322" s="15" t="s">
         <v>8</v>
       </c>
@@ -8248,7 +8248,7 @@
       <c r="I322" s="19"/>
       <c r="J322" s="20"/>
     </row>
-    <row r="323" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="323" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B323" s="15" t="s">
         <v>8</v>
       </c>
@@ -8271,7 +8271,7 @@
       <c r="I323" s="19"/>
       <c r="J323" s="20"/>
     </row>
-    <row r="324" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="324" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B324" s="15" t="s">
         <v>8</v>
       </c>
@@ -8294,7 +8294,7 @@
       <c r="I324" s="19"/>
       <c r="J324" s="20"/>
     </row>
-    <row r="325" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="325" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B325" s="15" t="s">
         <v>8</v>
       </c>
@@ -8317,7 +8317,7 @@
       <c r="I325" s="19"/>
       <c r="J325" s="20"/>
     </row>
-    <row r="326" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="326" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B326" s="15" t="s">
         <v>8</v>
       </c>
@@ -8340,7 +8340,7 @@
       <c r="I326" s="19"/>
       <c r="J326" s="20"/>
     </row>
-    <row r="327" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="327" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B327" s="15" t="s">
         <v>8</v>
       </c>
@@ -8363,7 +8363,7 @@
       <c r="I327" s="19"/>
       <c r="J327" s="20"/>
     </row>
-    <row r="328" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="328" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B328" s="15" t="s">
         <v>8</v>
       </c>
@@ -8386,7 +8386,7 @@
       <c r="I328" s="19"/>
       <c r="J328" s="20"/>
     </row>
-    <row r="329" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="329" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B329" s="15" t="s">
         <v>8</v>
       </c>
@@ -8409,7 +8409,7 @@
       <c r="I329" s="19"/>
       <c r="J329" s="20"/>
     </row>
-    <row r="330" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="330" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B330" s="15" t="s">
         <v>8</v>
       </c>
@@ -8432,7 +8432,7 @@
       <c r="I330" s="19"/>
       <c r="J330" s="20"/>
     </row>
-    <row r="331" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="331" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B331" s="15" t="s">
         <v>8</v>
       </c>
@@ -8455,7 +8455,7 @@
       <c r="I331" s="19"/>
       <c r="J331" s="20"/>
     </row>
-    <row r="332" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="332" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B332" s="15" t="s">
         <v>8</v>
       </c>
@@ -8478,7 +8478,7 @@
       <c r="I332" s="19"/>
       <c r="J332" s="20"/>
     </row>
-    <row r="333" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="333" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B333" s="15" t="s">
         <v>8</v>
       </c>
@@ -8501,7 +8501,7 @@
       <c r="I333" s="19"/>
       <c r="J333" s="20"/>
     </row>
-    <row r="334" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="334" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B334" s="15" t="s">
         <v>8</v>
       </c>
@@ -8524,7 +8524,7 @@
       <c r="I334" s="19"/>
       <c r="J334" s="20"/>
     </row>
-    <row r="335" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="335" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B335" s="15" t="s">
         <v>8</v>
       </c>
@@ -8547,7 +8547,7 @@
       <c r="I335" s="19"/>
       <c r="J335" s="20"/>
     </row>
-    <row r="336" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="336" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B336" s="15" t="s">
         <v>8</v>
       </c>
@@ -8570,7 +8570,7 @@
       <c r="I336" s="19"/>
       <c r="J336" s="20"/>
     </row>
-    <row r="337" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="337" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B337" s="15" t="s">
         <v>8</v>
       </c>
@@ -8593,7 +8593,7 @@
       <c r="I337" s="19"/>
       <c r="J337" s="20"/>
     </row>
-    <row r="338" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="338" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B338" s="15" t="s">
         <v>8</v>
       </c>
@@ -8616,7 +8616,7 @@
       <c r="I338" s="19"/>
       <c r="J338" s="20"/>
     </row>
-    <row r="339" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="339" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B339" s="15" t="s">
         <v>8</v>
       </c>
@@ -8639,7 +8639,7 @@
       <c r="I339" s="19"/>
       <c r="J339" s="20"/>
     </row>
-    <row r="340" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="340" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B340" s="15" t="s">
         <v>8</v>
       </c>
@@ -8662,7 +8662,7 @@
       <c r="I340" s="19"/>
       <c r="J340" s="20"/>
     </row>
-    <row r="341" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="341" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B341" s="15" t="s">
         <v>8</v>
       </c>
@@ -8685,7 +8685,7 @@
       <c r="I341" s="19"/>
       <c r="J341" s="20"/>
     </row>
-    <row r="342" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="342" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B342" s="15" t="s">
         <v>8</v>
       </c>
@@ -8708,7 +8708,7 @@
       <c r="I342" s="19"/>
       <c r="J342" s="20"/>
     </row>
-    <row r="343" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="343" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B343" s="15" t="s">
         <v>8</v>
       </c>
@@ -8731,7 +8731,7 @@
       <c r="I343" s="19"/>
       <c r="J343" s="20"/>
     </row>
-    <row r="344" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="344" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B344" s="15" t="s">
         <v>8</v>
       </c>
@@ -8754,7 +8754,7 @@
       <c r="I344" s="19"/>
       <c r="J344" s="20"/>
     </row>
-    <row r="345" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="345" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B345" s="15" t="s">
         <v>8</v>
       </c>
@@ -8777,7 +8777,7 @@
       <c r="I345" s="19"/>
       <c r="J345" s="20"/>
     </row>
-    <row r="346" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="346" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B346" s="15" t="s">
         <v>8</v>
       </c>
@@ -8800,7 +8800,7 @@
       <c r="I346" s="19"/>
       <c r="J346" s="20"/>
     </row>
-    <row r="347" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="347" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B347" s="15" t="s">
         <v>8</v>
       </c>
@@ -8823,7 +8823,7 @@
       <c r="I347" s="19"/>
       <c r="J347" s="20"/>
     </row>
-    <row r="348" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="348" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B348" s="15" t="s">
         <v>8</v>
       </c>
@@ -8846,7 +8846,7 @@
       <c r="I348" s="19"/>
       <c r="J348" s="20"/>
     </row>
-    <row r="349" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="349" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B349" s="15" t="s">
         <v>8</v>
       </c>
@@ -8869,7 +8869,7 @@
       <c r="I349" s="19"/>
       <c r="J349" s="20"/>
     </row>
-    <row r="350" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="350" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B350" s="15" t="s">
         <v>8</v>
       </c>
@@ -8892,7 +8892,7 @@
       <c r="I350" s="19"/>
       <c r="J350" s="20"/>
     </row>
-    <row r="351" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="351" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B351" s="15" t="s">
         <v>8</v>
       </c>
@@ -8915,7 +8915,7 @@
       <c r="I351" s="19"/>
       <c r="J351" s="20"/>
     </row>
-    <row r="352" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="352" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B352" s="15" t="s">
         <v>8</v>
       </c>
@@ -8938,7 +8938,7 @@
       <c r="I352" s="19"/>
       <c r="J352" s="20"/>
     </row>
-    <row r="353" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="353" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B353" s="15" t="s">
         <v>8</v>
       </c>
@@ -8961,7 +8961,7 @@
       <c r="I353" s="19"/>
       <c r="J353" s="20"/>
     </row>
-    <row r="354" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="354" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B354" s="15" t="s">
         <v>8</v>
       </c>
@@ -8984,7 +8984,7 @@
       <c r="I354" s="19"/>
       <c r="J354" s="20"/>
     </row>
-    <row r="355" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="355" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B355" s="15" t="s">
         <v>8</v>
       </c>
@@ -9007,7 +9007,7 @@
       <c r="I355" s="19"/>
       <c r="J355" s="20"/>
     </row>
-    <row r="356" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="356" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B356" s="15" t="s">
         <v>8</v>
       </c>
@@ -9030,7 +9030,7 @@
       <c r="I356" s="19"/>
       <c r="J356" s="20"/>
     </row>
-    <row r="357" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="357" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B357" s="15" t="s">
         <v>8</v>
       </c>
@@ -9053,7 +9053,7 @@
       <c r="I357" s="19"/>
       <c r="J357" s="20"/>
     </row>
-    <row r="358" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="358" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B358" s="15" t="s">
         <v>8</v>
       </c>
@@ -9076,7 +9076,7 @@
       <c r="I358" s="19"/>
       <c r="J358" s="20"/>
     </row>
-    <row r="359" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="359" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B359" s="15" t="s">
         <v>8</v>
       </c>
@@ -9099,7 +9099,7 @@
       <c r="I359" s="19"/>
       <c r="J359" s="20"/>
     </row>
-    <row r="360" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="360" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B360" s="15" t="s">
         <v>8</v>
       </c>
@@ -9122,7 +9122,7 @@
       <c r="I360" s="19"/>
       <c r="J360" s="20"/>
     </row>
-    <row r="361" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="361" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B361" s="15" t="s">
         <v>8</v>
       </c>
@@ -9145,7 +9145,7 @@
       <c r="I361" s="19"/>
       <c r="J361" s="20"/>
     </row>
-    <row r="362" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="362" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B362" s="15" t="s">
         <v>8</v>
       </c>
@@ -9168,7 +9168,7 @@
       <c r="I362" s="19"/>
       <c r="J362" s="20"/>
     </row>
-    <row r="363" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="363" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B363" s="15" t="s">
         <v>8</v>
       </c>
@@ -9191,7 +9191,7 @@
       <c r="I363" s="19"/>
       <c r="J363" s="20"/>
     </row>
-    <row r="364" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="364" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B364" s="15" t="s">
         <v>8</v>
       </c>
@@ -9214,7 +9214,7 @@
       <c r="I364" s="19"/>
       <c r="J364" s="20"/>
     </row>
-    <row r="365" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="365" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B365" s="15" t="s">
         <v>8</v>
       </c>
@@ -9237,7 +9237,7 @@
       <c r="I365" s="19"/>
       <c r="J365" s="20"/>
     </row>
-    <row r="366" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="366" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B366" s="15" t="s">
         <v>8</v>
       </c>
@@ -9260,7 +9260,7 @@
       <c r="I366" s="19"/>
       <c r="J366" s="20"/>
     </row>
-    <row r="367" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="367" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B367" s="15" t="s">
         <v>8</v>
       </c>
@@ -9283,7 +9283,7 @@
       <c r="I367" s="19"/>
       <c r="J367" s="20"/>
     </row>
-    <row r="368" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="368" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B368" s="15" t="s">
         <v>8</v>
       </c>
@@ -9306,7 +9306,7 @@
       <c r="I368" s="19"/>
       <c r="J368" s="20"/>
     </row>
-    <row r="369" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="369" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B369" s="15" t="s">
         <v>8</v>
       </c>
@@ -9329,7 +9329,7 @@
       <c r="I369" s="19"/>
       <c r="J369" s="20"/>
     </row>
-    <row r="370" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="370" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B370" s="15" t="s">
         <v>8</v>
       </c>
@@ -9352,7 +9352,7 @@
       <c r="I370" s="19"/>
       <c r="J370" s="20"/>
     </row>
-    <row r="371" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="371" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B371" s="15" t="s">
         <v>8</v>
       </c>
@@ -9375,7 +9375,7 @@
       <c r="I371" s="19"/>
       <c r="J371" s="20"/>
     </row>
-    <row r="372" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="372" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B372" s="15" t="s">
         <v>8</v>
       </c>
@@ -9398,7 +9398,7 @@
       <c r="I372" s="19"/>
       <c r="J372" s="20"/>
     </row>
-    <row r="373" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="373" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B373" s="15" t="s">
         <v>8</v>
       </c>
@@ -9421,7 +9421,7 @@
       <c r="I373" s="19"/>
       <c r="J373" s="20"/>
     </row>
-    <row r="374" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="374" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B374" s="15" t="s">
         <v>8</v>
       </c>
@@ -9444,7 +9444,7 @@
       <c r="I374" s="19"/>
       <c r="J374" s="20"/>
     </row>
-    <row r="375" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="375" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B375" s="15" t="s">
         <v>8</v>
       </c>
@@ -9467,7 +9467,7 @@
       <c r="I375" s="19"/>
       <c r="J375" s="20"/>
     </row>
-    <row r="376" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="376" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B376" s="15" t="s">
         <v>8</v>
       </c>
@@ -9490,7 +9490,7 @@
       <c r="I376" s="19"/>
       <c r="J376" s="20"/>
     </row>
-    <row r="377" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="377" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B377" s="15" t="s">
         <v>8</v>
       </c>
@@ -9513,7 +9513,7 @@
       <c r="I377" s="19"/>
       <c r="J377" s="20"/>
     </row>
-    <row r="378" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="378" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B378" s="15" t="s">
         <v>8</v>
       </c>
@@ -9536,7 +9536,7 @@
       <c r="I378" s="19"/>
       <c r="J378" s="20"/>
     </row>
-    <row r="379" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="379" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B379" s="15" t="s">
         <v>8</v>
       </c>
@@ -9559,7 +9559,7 @@
       <c r="I379" s="19"/>
       <c r="J379" s="20"/>
     </row>
-    <row r="380" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="380" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B380" s="15" t="s">
         <v>8</v>
       </c>
@@ -9582,7 +9582,7 @@
       <c r="I380" s="19"/>
       <c r="J380" s="20"/>
     </row>
-    <row r="381" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="381" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B381" s="15" t="s">
         <v>8</v>
       </c>
@@ -9605,7 +9605,7 @@
       <c r="I381" s="19"/>
       <c r="J381" s="20"/>
     </row>
-    <row r="382" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="382" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B382" s="15" t="s">
         <v>8</v>
       </c>
@@ -9628,7 +9628,7 @@
       <c r="I382" s="19"/>
       <c r="J382" s="20"/>
     </row>
-    <row r="383" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="383" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B383" s="15" t="s">
         <v>8</v>
       </c>
@@ -9651,7 +9651,7 @@
       <c r="I383" s="19"/>
       <c r="J383" s="20"/>
     </row>
-    <row r="384" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="384" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B384" s="15" t="s">
         <v>8</v>
       </c>
@@ -9674,7 +9674,7 @@
       <c r="I384" s="19"/>
       <c r="J384" s="20"/>
     </row>
-    <row r="385" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="385" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B385" s="15" t="s">
         <v>8</v>
       </c>
@@ -9697,7 +9697,7 @@
       <c r="I385" s="19"/>
       <c r="J385" s="20"/>
     </row>
-    <row r="386" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="386" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B386" s="15" t="s">
         <v>8</v>
       </c>
@@ -9720,7 +9720,7 @@
       <c r="I386" s="19"/>
       <c r="J386" s="20"/>
     </row>
-    <row r="387" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="387" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B387" s="15" t="s">
         <v>8</v>
       </c>
@@ -9743,7 +9743,7 @@
       <c r="I387" s="19"/>
       <c r="J387" s="20"/>
     </row>
-    <row r="388" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="388" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B388" s="15" t="s">
         <v>8</v>
       </c>
@@ -9766,7 +9766,7 @@
       <c r="I388" s="19"/>
       <c r="J388" s="20"/>
     </row>
-    <row r="389" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="389" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B389" s="15" t="s">
         <v>8</v>
       </c>
@@ -9789,7 +9789,7 @@
       <c r="I389" s="19"/>
       <c r="J389" s="20"/>
     </row>
-    <row r="390" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="390" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B390" s="15" t="s">
         <v>8</v>
       </c>
@@ -9812,7 +9812,7 @@
       <c r="I390" s="19"/>
       <c r="J390" s="20"/>
     </row>
-    <row r="391" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="391" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B391" s="15" t="s">
         <v>8</v>
       </c>
@@ -9835,7 +9835,7 @@
       <c r="I391" s="19"/>
       <c r="J391" s="20"/>
     </row>
-    <row r="392" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="392" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B392" s="15" t="s">
         <v>8</v>
       </c>
@@ -9858,7 +9858,7 @@
       <c r="I392" s="19"/>
       <c r="J392" s="20"/>
     </row>
-    <row r="393" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="393" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B393" s="15" t="s">
         <v>8</v>
       </c>
@@ -9881,7 +9881,7 @@
       <c r="I393" s="19"/>
       <c r="J393" s="20"/>
     </row>
-    <row r="394" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="394" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B394" s="15" t="s">
         <v>8</v>
       </c>
@@ -9904,7 +9904,7 @@
       <c r="I394" s="19"/>
       <c r="J394" s="20"/>
     </row>
-    <row r="395" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="395" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B395" s="15" t="s">
         <v>8</v>
       </c>
@@ -9927,7 +9927,7 @@
       <c r="I395" s="19"/>
       <c r="J395" s="20"/>
     </row>
-    <row r="396" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="396" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B396" s="15" t="s">
         <v>8</v>
       </c>
@@ -9950,7 +9950,7 @@
       <c r="I396" s="19"/>
       <c r="J396" s="20"/>
     </row>
-    <row r="397" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="397" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B397" s="15" t="s">
         <v>8</v>
       </c>
@@ -9973,7 +9973,7 @@
       <c r="I397" s="19"/>
       <c r="J397" s="20"/>
     </row>
-    <row r="398" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="398" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B398" s="15" t="s">
         <v>8</v>
       </c>
@@ -9996,7 +9996,7 @@
       <c r="I398" s="19"/>
       <c r="J398" s="20"/>
     </row>
-    <row r="399" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="399" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B399" s="15" t="s">
         <v>8</v>
       </c>
@@ -10019,7 +10019,7 @@
       <c r="I399" s="19"/>
       <c r="J399" s="20"/>
     </row>
-    <row r="400" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="400" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B400" s="15" t="s">
         <v>8</v>
       </c>
@@ -10042,7 +10042,7 @@
       <c r="I400" s="19"/>
       <c r="J400" s="20"/>
     </row>
-    <row r="401" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="401" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B401" s="15" t="s">
         <v>8</v>
       </c>
@@ -10065,7 +10065,7 @@
       <c r="I401" s="19"/>
       <c r="J401" s="20"/>
     </row>
-    <row r="402" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="402" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B402" s="15" t="s">
         <v>8</v>
       </c>
@@ -10088,7 +10088,7 @@
       <c r="I402" s="19"/>
       <c r="J402" s="20"/>
     </row>
-    <row r="403" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="403" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B403" s="15" t="s">
         <v>8</v>
       </c>
@@ -10111,7 +10111,7 @@
       <c r="I403" s="19"/>
       <c r="J403" s="20"/>
     </row>
-    <row r="404" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="404" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B404" s="15" t="s">
         <v>8</v>
       </c>
@@ -10134,7 +10134,7 @@
       <c r="I404" s="19"/>
       <c r="J404" s="20"/>
     </row>
-    <row r="405" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="405" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B405" s="15" t="s">
         <v>8</v>
       </c>
@@ -10157,7 +10157,7 @@
       <c r="I405" s="19"/>
       <c r="J405" s="20"/>
     </row>
-    <row r="406" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="406" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B406" s="15" t="s">
         <v>8</v>
       </c>
@@ -10180,7 +10180,7 @@
       <c r="I406" s="19"/>
       <c r="J406" s="20"/>
     </row>
-    <row r="407" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="407" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B407" s="15" t="s">
         <v>8</v>
       </c>
@@ -10203,7 +10203,7 @@
       <c r="I407" s="19"/>
       <c r="J407" s="20"/>
     </row>
-    <row r="408" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="408" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B408" s="15" t="s">
         <v>8</v>
       </c>
@@ -10226,7 +10226,7 @@
       <c r="I408" s="19"/>
       <c r="J408" s="20"/>
     </row>
-    <row r="409" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="409" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B409" s="15" t="s">
         <v>8</v>
       </c>
@@ -10249,7 +10249,7 @@
       <c r="I409" s="19"/>
       <c r="J409" s="20"/>
     </row>
-    <row r="410" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="410" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B410" s="15" t="s">
         <v>8</v>
       </c>
@@ -10272,7 +10272,7 @@
       <c r="I410" s="19"/>
       <c r="J410" s="20"/>
     </row>
-    <row r="411" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="411" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B411" s="15" t="s">
         <v>8</v>
       </c>
@@ -10295,7 +10295,7 @@
       <c r="I411" s="19"/>
       <c r="J411" s="20"/>
     </row>
-    <row r="412" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="412" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B412" s="15" t="s">
         <v>8</v>
       </c>
@@ -10318,7 +10318,7 @@
       <c r="I412" s="19"/>
       <c r="J412" s="20"/>
     </row>
-    <row r="413" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="413" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B413" s="15" t="s">
         <v>8</v>
       </c>
@@ -10341,7 +10341,7 @@
       <c r="I413" s="19"/>
       <c r="J413" s="20"/>
     </row>
-    <row r="414" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="414" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B414" s="15" t="s">
         <v>8</v>
       </c>
@@ -10364,7 +10364,7 @@
       <c r="I414" s="19"/>
       <c r="J414" s="20"/>
     </row>
-    <row r="415" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="415" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B415" s="15" t="s">
         <v>8</v>
       </c>
@@ -10387,7 +10387,7 @@
       <c r="I415" s="19"/>
       <c r="J415" s="20"/>
     </row>
-    <row r="416" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="416" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B416" s="15" t="s">
         <v>8</v>
       </c>
@@ -10410,7 +10410,7 @@
       <c r="I416" s="19"/>
       <c r="J416" s="20"/>
     </row>
-    <row r="417" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="417" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B417" s="15" t="s">
         <v>8</v>
       </c>
@@ -10433,7 +10433,7 @@
       <c r="I417" s="19"/>
       <c r="J417" s="20"/>
     </row>
-    <row r="418" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="418" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B418" s="15" t="s">
         <v>8</v>
       </c>
@@ -10456,7 +10456,7 @@
       <c r="I418" s="19"/>
       <c r="J418" s="20"/>
     </row>
-    <row r="419" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="419" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B419" s="15" t="s">
         <v>8</v>
       </c>
@@ -10479,7 +10479,7 @@
       <c r="I419" s="19"/>
       <c r="J419" s="20"/>
     </row>
-    <row r="420" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="420" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B420" s="15" t="s">
         <v>8</v>
       </c>
@@ -10502,7 +10502,7 @@
       <c r="I420" s="19"/>
       <c r="J420" s="20"/>
     </row>
-    <row r="421" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="421" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B421" s="15" t="s">
         <v>8</v>
       </c>
@@ -10525,7 +10525,7 @@
       <c r="I421" s="19"/>
       <c r="J421" s="20"/>
     </row>
-    <row r="422" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="422" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B422" s="15" t="s">
         <v>8</v>
       </c>
@@ -10548,7 +10548,7 @@
       <c r="I422" s="19"/>
       <c r="J422" s="20"/>
     </row>
-    <row r="423" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="423" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B423" s="15" t="s">
         <v>8</v>
       </c>
@@ -10571,7 +10571,7 @@
       <c r="I423" s="19"/>
       <c r="J423" s="20"/>
     </row>
-    <row r="424" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="424" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B424" s="15" t="s">
         <v>8</v>
       </c>
@@ -10594,7 +10594,7 @@
       <c r="I424" s="19"/>
       <c r="J424" s="20"/>
     </row>
-    <row r="425" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="425" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B425" s="15" t="s">
         <v>8</v>
       </c>
@@ -10617,7 +10617,7 @@
       <c r="I425" s="19"/>
       <c r="J425" s="20"/>
     </row>
-    <row r="426" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="426" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B426" s="15" t="s">
         <v>8</v>
       </c>
@@ -10640,7 +10640,7 @@
       <c r="I426" s="19"/>
       <c r="J426" s="20"/>
     </row>
-    <row r="427" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="427" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B427" s="15" t="s">
         <v>8</v>
       </c>
@@ -10663,7 +10663,7 @@
       <c r="I427" s="19"/>
       <c r="J427" s="20"/>
     </row>
-    <row r="428" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="428" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B428" s="15" t="s">
         <v>8</v>
       </c>
@@ -10686,7 +10686,7 @@
       <c r="I428" s="19"/>
       <c r="J428" s="20"/>
     </row>
-    <row r="429" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="429" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B429" s="15" t="s">
         <v>8</v>
       </c>
@@ -10709,7 +10709,7 @@
       <c r="I429" s="19"/>
       <c r="J429" s="20"/>
     </row>
-    <row r="430" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="430" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B430" s="15" t="s">
         <v>8</v>
       </c>
@@ -10732,7 +10732,7 @@
       <c r="I430" s="19"/>
       <c r="J430" s="20"/>
     </row>
-    <row r="431" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="431" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B431" s="15" t="s">
         <v>8</v>
       </c>
@@ -10755,7 +10755,7 @@
       <c r="I431" s="19"/>
       <c r="J431" s="20"/>
     </row>
-    <row r="432" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="432" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B432" s="15" t="s">
         <v>8</v>
       </c>
@@ -10778,7 +10778,7 @@
       <c r="I432" s="19"/>
       <c r="J432" s="20"/>
     </row>
-    <row r="433" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="433" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B433" s="15" t="s">
         <v>8</v>
       </c>
@@ -10801,7 +10801,7 @@
       <c r="I433" s="19"/>
       <c r="J433" s="20"/>
     </row>
-    <row r="434" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="434" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B434" s="15" t="s">
         <v>8</v>
       </c>
@@ -10824,7 +10824,7 @@
       <c r="I434" s="19"/>
       <c r="J434" s="20"/>
     </row>
-    <row r="435" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="435" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B435" s="15" t="s">
         <v>8</v>
       </c>
@@ -10847,7 +10847,7 @@
       <c r="I435" s="19"/>
       <c r="J435" s="20"/>
     </row>
-    <row r="436" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="436" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B436" s="15" t="s">
         <v>8</v>
       </c>
@@ -10870,7 +10870,7 @@
       <c r="I436" s="19"/>
       <c r="J436" s="20"/>
     </row>
-    <row r="437" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="437" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B437" s="15" t="s">
         <v>8</v>
       </c>
@@ -10893,7 +10893,7 @@
       <c r="I437" s="19"/>
       <c r="J437" s="20"/>
     </row>
-    <row r="438" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="438" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B438" s="15" t="s">
         <v>8</v>
       </c>
@@ -10916,7 +10916,7 @@
       <c r="I438" s="19"/>
       <c r="J438" s="20"/>
     </row>
-    <row r="439" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="439" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B439" s="15" t="s">
         <v>8</v>
       </c>
@@ -10939,7 +10939,7 @@
       <c r="I439" s="19"/>
       <c r="J439" s="20"/>
     </row>
-    <row r="440" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="440" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B440" s="15" t="s">
         <v>8</v>
       </c>
@@ -10962,7 +10962,7 @@
       <c r="I440" s="19"/>
       <c r="J440" s="20"/>
     </row>
-    <row r="441" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="441" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B441" s="15" t="s">
         <v>8</v>
       </c>
@@ -10985,7 +10985,7 @@
       <c r="I441" s="19"/>
       <c r="J441" s="20"/>
     </row>
-    <row r="442" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="442" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B442" s="15" t="s">
         <v>8</v>
       </c>
@@ -11008,7 +11008,7 @@
       <c r="I442" s="19"/>
       <c r="J442" s="20"/>
     </row>
-    <row r="443" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="443" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B443" s="15" t="s">
         <v>8</v>
       </c>
@@ -11031,7 +11031,7 @@
       <c r="I443" s="19"/>
       <c r="J443" s="20"/>
     </row>
-    <row r="444" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="444" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B444" s="15" t="s">
         <v>8</v>
       </c>
@@ -11054,7 +11054,7 @@
       <c r="I444" s="19"/>
       <c r="J444" s="20"/>
     </row>
-    <row r="445" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="445" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B445" s="15" t="s">
         <v>8</v>
       </c>
@@ -11077,7 +11077,7 @@
       <c r="I445" s="19"/>
       <c r="J445" s="20"/>
     </row>
-    <row r="446" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="446" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B446" s="15" t="s">
         <v>8</v>
       </c>
@@ -11100,7 +11100,7 @@
       <c r="I446" s="19"/>
       <c r="J446" s="20"/>
     </row>
-    <row r="447" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="447" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B447" s="15" t="s">
         <v>8</v>
       </c>
@@ -11123,7 +11123,7 @@
       <c r="I447" s="19"/>
       <c r="J447" s="20"/>
     </row>
-    <row r="448" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="448" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B448" s="15" t="s">
         <v>8</v>
       </c>
@@ -11146,7 +11146,7 @@
       <c r="I448" s="19"/>
       <c r="J448" s="20"/>
     </row>
-    <row r="449" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="449" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B449" s="15" t="s">
         <v>8</v>
       </c>
@@ -11169,7 +11169,7 @@
       <c r="I449" s="19"/>
       <c r="J449" s="20"/>
     </row>
-    <row r="450" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="450" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B450" s="15" t="s">
         <v>8</v>
       </c>
@@ -11192,7 +11192,7 @@
       <c r="I450" s="19"/>
       <c r="J450" s="20"/>
     </row>
-    <row r="451" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="451" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B451" s="15" t="s">
         <v>8</v>
       </c>
@@ -11215,7 +11215,7 @@
       <c r="I451" s="19"/>
       <c r="J451" s="20"/>
     </row>
-    <row r="452" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="452" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B452" s="15" t="s">
         <v>8</v>
       </c>
@@ -11238,7 +11238,7 @@
       <c r="I452" s="19"/>
       <c r="J452" s="20"/>
     </row>
-    <row r="453" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="453" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B453" s="15" t="s">
         <v>8</v>
       </c>
@@ -11261,7 +11261,7 @@
       <c r="I453" s="19"/>
       <c r="J453" s="20"/>
     </row>
-    <row r="454" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="454" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B454" s="15" t="s">
         <v>8</v>
       </c>
@@ -11284,7 +11284,7 @@
       <c r="I454" s="19"/>
       <c r="J454" s="20"/>
     </row>
-    <row r="455" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="455" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B455" s="15" t="s">
         <v>8</v>
       </c>
@@ -11307,7 +11307,7 @@
       <c r="I455" s="19"/>
       <c r="J455" s="20"/>
     </row>
-    <row r="456" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="456" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B456" s="15" t="s">
         <v>8</v>
       </c>
@@ -11330,7 +11330,7 @@
       <c r="I456" s="19"/>
       <c r="J456" s="20"/>
     </row>
-    <row r="457" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="457" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B457" s="15" t="s">
         <v>8</v>
       </c>
@@ -11353,7 +11353,7 @@
       <c r="I457" s="19"/>
       <c r="J457" s="20"/>
     </row>
-    <row r="458" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="458" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B458" s="15" t="s">
         <v>8</v>
       </c>
@@ -11376,7 +11376,7 @@
       <c r="I458" s="19"/>
       <c r="J458" s="20"/>
     </row>
-    <row r="459" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="459" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B459" s="15" t="s">
         <v>8</v>
       </c>
@@ -11399,7 +11399,7 @@
       <c r="I459" s="19"/>
       <c r="J459" s="20"/>
     </row>
-    <row r="460" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="460" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B460" s="21" t="s">
         <v>8</v>
       </c>
@@ -11422,7 +11422,7 @@
       <c r="I460" s="25"/>
       <c r="J460" s="26"/>
     </row>
-    <row r="465" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="465" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B465" s="32" t="s">
         <v>84</v>
       </c>
@@ -11433,7 +11433,7 @@
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
     </row>
-    <row r="466" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="466" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B466" s="32" t="s">
         <v>83</v>
       </c>
